--- a/Proje/Machine Learning Model/model5/final_ready_simplified_categorical_target.xlsx
+++ b/Proje/Machine Learning Model/model5/final_ready_simplified_categorical_target.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmi\Desktop\Univercity\Diger\Android_AI_Assistant\Proje\Machine Learning Model\model5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE742A4-1FFD-43DA-AF5A-B1E1B2B78B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9E542C-B66F-494B-A39F-62C93B2A566F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13630,10 +13630,10 @@
     </row>
     <row r="543" spans="1:6" ht="14.4">
       <c r="A543" s="2" t="s">
-        <v>581</v>
+        <v>872</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>8</v>
@@ -13650,10 +13650,10 @@
     </row>
     <row r="544" spans="1:6" ht="14.4">
       <c r="A544" s="2" t="s">
-        <v>582</v>
+        <v>873</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>8</v>
@@ -13670,10 +13670,10 @@
     </row>
     <row r="545" spans="1:6" ht="14.4">
       <c r="A545" s="2" t="s">
-        <v>583</v>
+        <v>874</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C545" s="2" t="s">
         <v>8</v>
@@ -13690,13 +13690,13 @@
     </row>
     <row r="546" spans="1:6" ht="14.4">
       <c r="A546" s="2" t="s">
-        <v>584</v>
+        <v>875</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D546" s="2" t="s">
         <v>536</v>
@@ -13710,13 +13710,13 @@
     </row>
     <row r="547" spans="1:6" ht="14.4">
       <c r="A547" s="2" t="s">
-        <v>585</v>
+        <v>876</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D547" s="2" t="s">
         <v>536</v>
@@ -13730,10 +13730,10 @@
     </row>
     <row r="548" spans="1:6" ht="14.4">
       <c r="A548" s="2" t="s">
-        <v>586</v>
+        <v>877</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>8</v>
@@ -13742,18 +13742,18 @@
         <v>536</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F548" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="549" spans="1:6" ht="14.4">
       <c r="A549" s="2" t="s">
-        <v>587</v>
+        <v>878</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>8</v>
@@ -13762,18 +13762,18 @@
         <v>536</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F549" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="550" spans="1:6" ht="14.4">
       <c r="A550" s="2" t="s">
-        <v>588</v>
+        <v>879</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>8</v>
@@ -13782,58 +13782,58 @@
         <v>536</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F550" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="551" spans="1:6" ht="14.4">
       <c r="A551" s="2" t="s">
-        <v>589</v>
+        <v>880</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D551" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F551" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="552" spans="1:6" ht="14.4">
       <c r="A552" s="2" t="s">
-        <v>590</v>
+        <v>881</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D552" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F552" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="553" spans="1:6" ht="14.4">
       <c r="A553" s="2" t="s">
-        <v>591</v>
+        <v>882</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>8</v>
@@ -13842,18 +13842,18 @@
         <v>536</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="F553" s="2" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
     </row>
     <row r="554" spans="1:6" ht="14.4">
       <c r="A554" s="2" t="s">
-        <v>592</v>
+        <v>883</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>8</v>
@@ -13862,18 +13862,18 @@
         <v>536</v>
       </c>
       <c r="E554" s="2" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="F554" s="2" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
     </row>
     <row r="555" spans="1:6" ht="14.4">
       <c r="A555" s="2" t="s">
-        <v>593</v>
+        <v>884</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>8</v>
@@ -13882,58 +13882,58 @@
         <v>536</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="F555" s="2" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
     </row>
     <row r="556" spans="1:6" ht="14.4">
       <c r="A556" s="2" t="s">
-        <v>594</v>
+        <v>885</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D556" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="F556" s="2" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
     </row>
     <row r="557" spans="1:6" ht="14.4">
       <c r="A557" s="2" t="s">
-        <v>595</v>
+        <v>886</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D557" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="F557" s="2" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="558" spans="1:6" ht="14.4">
       <c r="A558" s="2" t="s">
-        <v>596</v>
+        <v>887</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C558" s="2" t="s">
         <v>8</v>
@@ -13942,18 +13942,18 @@
         <v>536</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="F558" s="2" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="559" spans="1:6" ht="14.4">
       <c r="A559" s="2" t="s">
-        <v>597</v>
+        <v>888</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>8</v>
@@ -13962,18 +13962,18 @@
         <v>536</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="F559" s="2" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="560" spans="1:6" ht="14.4">
       <c r="A560" s="2" t="s">
-        <v>598</v>
+        <v>889</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C560" s="2" t="s">
         <v>8</v>
@@ -13982,41 +13982,41 @@
         <v>536</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="F560" s="2" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="561" spans="1:6" ht="14.4">
       <c r="A561" s="2" t="s">
-        <v>599</v>
+        <v>890</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D561" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E561" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="F561" s="2" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="562" spans="1:6" ht="14.4">
       <c r="A562" s="2" t="s">
-        <v>600</v>
+        <v>891</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D562" s="2" t="s">
         <v>536</v>
@@ -14030,167 +14030,167 @@
     </row>
     <row r="563" spans="1:6" ht="14.4">
       <c r="A563" s="2" t="s">
-        <v>601</v>
+        <v>581</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D563" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F563" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="564" spans="1:6" ht="14.4">
       <c r="A564" s="2" t="s">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D564" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F564" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="565" spans="1:6" ht="14.4">
       <c r="A565" s="2" t="s">
-        <v>603</v>
+        <v>583</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D565" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F565" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="566" spans="1:6" ht="14.4">
       <c r="A566" s="2" t="s">
-        <v>604</v>
+        <v>584</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D566" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F566" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="567" spans="1:6" ht="14.4">
       <c r="A567" s="2" t="s">
-        <v>605</v>
+        <v>585</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D567" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E567" s="2" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="F567" s="2" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
     </row>
     <row r="568" spans="1:6" ht="14.4">
       <c r="A568" s="2" t="s">
-        <v>606</v>
+        <v>586</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D568" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="F568" s="2" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
     </row>
     <row r="569" spans="1:6" ht="14.4">
       <c r="A569" s="2" t="s">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D569" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E569" s="2" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="F569" s="2" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
     </row>
     <row r="570" spans="1:6" ht="14.4">
       <c r="A570" s="2" t="s">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D570" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E570" s="2" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="F570" s="2" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
     </row>
     <row r="571" spans="1:6" ht="14.4">
       <c r="A571" s="2" t="s">
-        <v>609</v>
+        <v>589</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>47</v>
@@ -14201,14 +14201,16 @@
       <c r="D571" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E571" s="2"/>
+      <c r="E571" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F571" s="2" t="s">
-        <v>571</v>
+        <v>545</v>
       </c>
     </row>
     <row r="572" spans="1:6" ht="14.4">
       <c r="A572" s="2" t="s">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>47</v>
@@ -14219,14 +14221,16 @@
       <c r="D572" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E572" s="2"/>
+      <c r="E572" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F572" s="2" t="s">
-        <v>571</v>
+        <v>545</v>
       </c>
     </row>
     <row r="573" spans="1:6" ht="14.4">
       <c r="A573" s="2" t="s">
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>47</v>
@@ -14237,50 +14241,56 @@
       <c r="D573" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E573" s="2"/>
+      <c r="E573" s="2" t="s">
+        <v>551</v>
+      </c>
       <c r="F573" s="2" t="s">
-        <v>571</v>
+        <v>552</v>
       </c>
     </row>
     <row r="574" spans="1:6" ht="14.4">
       <c r="A574" s="2" t="s">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D574" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E574" s="2"/>
+      <c r="E574" s="2" t="s">
+        <v>551</v>
+      </c>
       <c r="F574" s="2" t="s">
-        <v>571</v>
+        <v>552</v>
       </c>
     </row>
     <row r="575" spans="1:6" ht="14.4">
       <c r="A575" s="2" t="s">
-        <v>613</v>
+        <v>593</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D575" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E575" s="2"/>
+      <c r="E575" s="2" t="s">
+        <v>551</v>
+      </c>
       <c r="F575" s="2" t="s">
-        <v>571</v>
+        <v>552</v>
       </c>
     </row>
     <row r="576" spans="1:6" ht="14.4">
       <c r="A576" s="2" t="s">
-        <v>614</v>
+        <v>594</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>47</v>
@@ -14291,14 +14301,16 @@
       <c r="D576" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E576" s="2"/>
+      <c r="E576" s="2" t="s">
+        <v>551</v>
+      </c>
       <c r="F576" s="2" t="s">
-        <v>571</v>
+        <v>552</v>
       </c>
     </row>
     <row r="577" spans="1:6" ht="14.4">
       <c r="A577" s="2" t="s">
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>47</v>
@@ -14310,15 +14322,15 @@
         <v>536</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="F577" s="2" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
     </row>
     <row r="578" spans="1:6" ht="14.4">
       <c r="A578" s="2" t="s">
-        <v>616</v>
+        <v>596</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>47</v>
@@ -14330,58 +14342,58 @@
         <v>536</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="F578" s="2" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
     </row>
     <row r="579" spans="1:6" ht="14.4">
       <c r="A579" s="2" t="s">
-        <v>617</v>
+        <v>597</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D579" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="F579" s="2" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
     </row>
     <row r="580" spans="1:6" ht="14.4">
       <c r="A580" s="2" t="s">
-        <v>618</v>
+        <v>598</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D580" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="F580" s="2" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
     </row>
     <row r="581" spans="1:6" ht="14.4">
       <c r="A581" s="2" t="s">
-        <v>619</v>
+        <v>599</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C581" s="2" t="s">
         <v>8</v>
@@ -14398,93 +14410,93 @@
     </row>
     <row r="582" spans="1:6" ht="14.4">
       <c r="A582" s="2" t="s">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D582" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="F582" s="2" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="583" spans="1:6" ht="14.4">
       <c r="A583" s="2" t="s">
-        <v>621</v>
+        <v>601</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D583" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="F583" s="2" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="584" spans="1:6" ht="14.4">
       <c r="A584" s="2" t="s">
-        <v>622</v>
+        <v>602</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D584" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="F584" s="2" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="585" spans="1:6" ht="14.4">
       <c r="A585" s="2" t="s">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D585" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="F585" s="2" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="586" spans="1:6" ht="14.4">
       <c r="A586" s="2" t="s">
-        <v>624</v>
+        <v>604</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D586" s="2" t="s">
         <v>536</v>
@@ -14498,73 +14510,73 @@
     </row>
     <row r="587" spans="1:6" ht="14.4">
       <c r="A587" s="2" t="s">
-        <v>625</v>
+        <v>605</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D587" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="F587" s="2" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
     </row>
     <row r="588" spans="1:6" ht="14.4">
       <c r="A588" s="2" t="s">
-        <v>626</v>
+        <v>606</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D588" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="F588" s="2" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
     </row>
     <row r="589" spans="1:6" ht="14.4">
       <c r="A589" s="2" t="s">
-        <v>627</v>
+        <v>607</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D589" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="F589" s="2" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
     </row>
     <row r="590" spans="1:6" ht="14.4">
       <c r="A590" s="2" t="s">
-        <v>628</v>
+        <v>608</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D590" s="2" t="s">
         <v>536</v>
@@ -14578,10 +14590,10 @@
     </row>
     <row r="591" spans="1:6" ht="14.4">
       <c r="A591" s="2" t="s">
-        <v>629</v>
+        <v>609</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C591" s="2" t="s">
         <v>8</v>
@@ -14589,19 +14601,17 @@
       <c r="D591" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E591" s="2" t="s">
-        <v>551</v>
-      </c>
+      <c r="E591" s="2"/>
       <c r="F591" s="2" t="s">
-        <v>552</v>
+        <v>571</v>
       </c>
     </row>
     <row r="592" spans="1:6" ht="14.4">
       <c r="A592" s="2" t="s">
-        <v>630</v>
+        <v>610</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C592" s="2" t="s">
         <v>8</v>
@@ -14609,19 +14619,17 @@
       <c r="D592" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E592" s="2" t="s">
-        <v>551</v>
-      </c>
+      <c r="E592" s="2"/>
       <c r="F592" s="2" t="s">
-        <v>552</v>
+        <v>571</v>
       </c>
     </row>
     <row r="593" spans="1:6" ht="14.4">
       <c r="A593" s="2" t="s">
-        <v>631</v>
+        <v>611</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C593" s="2" t="s">
         <v>8</v>
@@ -14629,59 +14637,53 @@
       <c r="D593" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E593" s="2" t="s">
-        <v>554</v>
-      </c>
+      <c r="E593" s="2"/>
       <c r="F593" s="2" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
     </row>
     <row r="594" spans="1:6" ht="14.4">
       <c r="A594" s="2" t="s">
-        <v>632</v>
+        <v>612</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D594" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E594" s="2" t="s">
-        <v>537</v>
-      </c>
+      <c r="E594" s="2"/>
       <c r="F594" s="2" t="s">
-        <v>538</v>
+        <v>571</v>
       </c>
     </row>
     <row r="595" spans="1:6" ht="14.4">
       <c r="A595" s="2" t="s">
-        <v>633</v>
+        <v>613</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D595" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E595" s="2" t="s">
-        <v>537</v>
-      </c>
+      <c r="E595" s="2"/>
       <c r="F595" s="2" t="s">
-        <v>538</v>
+        <v>571</v>
       </c>
     </row>
     <row r="596" spans="1:6" ht="14.4">
       <c r="A596" s="2" t="s">
-        <v>634</v>
+        <v>614</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>8</v>
@@ -14689,19 +14691,17 @@
       <c r="D596" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E596" s="2" t="s">
-        <v>537</v>
-      </c>
+      <c r="E596" s="2"/>
       <c r="F596" s="2" t="s">
-        <v>538</v>
+        <v>571</v>
       </c>
     </row>
     <row r="597" spans="1:6" ht="14.4">
       <c r="A597" s="2" t="s">
-        <v>635</v>
+        <v>615</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C597" s="2" t="s">
         <v>8</v>
@@ -14710,18 +14710,18 @@
         <v>536</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="F597" s="2" t="s">
-        <v>538</v>
+        <v>555</v>
       </c>
     </row>
     <row r="598" spans="1:6" ht="14.4">
       <c r="A598" s="2" t="s">
-        <v>636</v>
+        <v>616</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C598" s="2" t="s">
         <v>8</v>
@@ -14730,18 +14730,18 @@
         <v>536</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="F598" s="2" t="s">
-        <v>538</v>
+        <v>555</v>
       </c>
     </row>
     <row r="599" spans="1:6" ht="14.4">
       <c r="A599" s="2" t="s">
-        <v>637</v>
+        <v>617</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C599" s="2" t="s">
         <v>34</v>
@@ -14750,118 +14750,118 @@
         <v>536</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="F599" s="2" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
     </row>
     <row r="600" spans="1:6" ht="14.4">
       <c r="A600" s="2" t="s">
-        <v>638</v>
+        <v>618</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D600" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="F600" s="2" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
     </row>
     <row r="601" spans="1:6" ht="14.4">
       <c r="A601" s="2" t="s">
-        <v>639</v>
+        <v>892</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D601" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F601" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="602" spans="1:6" ht="14.4">
       <c r="A602" s="2" t="s">
-        <v>640</v>
+        <v>893</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D602" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F602" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="603" spans="1:6" ht="14.4">
       <c r="A603" s="2" t="s">
-        <v>641</v>
+        <v>894</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D603" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="F603" s="2" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
     </row>
     <row r="604" spans="1:6" ht="14.4">
       <c r="A604" s="2" t="s">
-        <v>642</v>
+        <v>895</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D604" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="F604" s="2" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
     </row>
     <row r="605" spans="1:6" ht="14.4">
       <c r="A605" s="2" t="s">
-        <v>643</v>
+        <v>896</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>40</v>
@@ -14870,38 +14870,38 @@
         <v>536</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="F605" s="2" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
     </row>
     <row r="606" spans="1:6" ht="14.4">
       <c r="A606" s="2" t="s">
-        <v>644</v>
+        <v>897</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D606" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="F606" s="2" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
     </row>
     <row r="607" spans="1:6" ht="14.4">
       <c r="A607" s="2" t="s">
-        <v>645</v>
+        <v>898</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C607" s="2" t="s">
         <v>8</v>
@@ -14909,17 +14909,19 @@
       <c r="D607" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E607" s="2"/>
+      <c r="E607" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F607" s="2" t="s">
-        <v>571</v>
+        <v>545</v>
       </c>
     </row>
     <row r="608" spans="1:6" ht="14.4">
       <c r="A608" s="2" t="s">
-        <v>646</v>
+        <v>899</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C608" s="2" t="s">
         <v>8</v>
@@ -14927,68 +14929,76 @@
       <c r="D608" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E608" s="2"/>
+      <c r="E608" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F608" s="2" t="s">
-        <v>571</v>
+        <v>545</v>
       </c>
     </row>
     <row r="609" spans="1:6" ht="14.4">
       <c r="A609" s="2" t="s">
-        <v>647</v>
+        <v>900</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D609" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E609" s="2"/>
+      <c r="E609" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F609" s="2" t="s">
-        <v>571</v>
+        <v>545</v>
       </c>
     </row>
     <row r="610" spans="1:6" ht="14.4">
       <c r="A610" s="2" t="s">
-        <v>648</v>
+        <v>901</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D610" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E610" s="2"/>
+      <c r="E610" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F610" s="2" t="s">
-        <v>571</v>
+        <v>545</v>
       </c>
     </row>
     <row r="611" spans="1:6" ht="14.4">
       <c r="A611" s="2" t="s">
-        <v>649</v>
+        <v>619</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D611" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E611" s="2"/>
+      <c r="E611" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="F611" s="2" t="s">
-        <v>571</v>
+        <v>538</v>
       </c>
     </row>
     <row r="612" spans="1:6" ht="14.4">
       <c r="A612" s="2" t="s">
-        <v>650</v>
+        <v>620</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>80</v>
@@ -14999,14 +15009,16 @@
       <c r="D612" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E612" s="2"/>
+      <c r="E612" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="F612" s="2" t="s">
-        <v>571</v>
+        <v>538</v>
       </c>
     </row>
     <row r="613" spans="1:6" ht="14.4">
       <c r="A613" s="2" t="s">
-        <v>651</v>
+        <v>621</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>80</v>
@@ -15018,15 +15030,15 @@
         <v>536</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="F613" s="2" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
     </row>
     <row r="614" spans="1:6" ht="14.4">
       <c r="A614" s="2" t="s">
-        <v>652</v>
+        <v>622</v>
       </c>
       <c r="B614" s="2" t="s">
         <v>80</v>
@@ -15038,814 +15050,886 @@
         <v>536</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="F614" s="2" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
     </row>
     <row r="615" spans="1:6" ht="14.4">
       <c r="A615" s="2" t="s">
-        <v>653</v>
+        <v>623</v>
       </c>
       <c r="B615" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D615" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="F615" s="2" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
     </row>
     <row r="616" spans="1:6" ht="14.4">
       <c r="A616" s="2" t="s">
-        <v>654</v>
+        <v>624</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C616" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D616" s="2" t="s">
         <v>536</v>
       </c>
       <c r="E616" s="2" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="F616" s="2" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
     </row>
     <row r="617" spans="1:6" ht="14.4">
       <c r="A617" s="2" t="s">
-        <v>655</v>
+        <v>625</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C617" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D617" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E617" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E617" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F617" s="2" t="s">
-        <v>657</v>
+        <v>545</v>
       </c>
     </row>
     <row r="618" spans="1:6" ht="14.4">
       <c r="A618" s="2" t="s">
-        <v>658</v>
+        <v>626</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C618" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D618" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E618" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E618" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F618" s="2" t="s">
-        <v>657</v>
+        <v>545</v>
       </c>
     </row>
     <row r="619" spans="1:6" ht="14.4">
       <c r="A619" s="2" t="s">
-        <v>659</v>
+        <v>627</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C619" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D619" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E619" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E619" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F619" s="2" t="s">
-        <v>657</v>
+        <v>545</v>
       </c>
     </row>
     <row r="620" spans="1:6" ht="14.4">
       <c r="A620" s="2" t="s">
-        <v>660</v>
+        <v>628</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D620" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E620" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E620" s="2" t="s">
+        <v>551</v>
+      </c>
       <c r="F620" s="2" t="s">
-        <v>657</v>
+        <v>552</v>
       </c>
     </row>
     <row r="621" spans="1:6" ht="14.4">
       <c r="A621" s="2" t="s">
-        <v>661</v>
+        <v>629</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C621" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D621" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E621" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E621" s="2" t="s">
+        <v>551</v>
+      </c>
       <c r="F621" s="2" t="s">
-        <v>657</v>
+        <v>552</v>
       </c>
     </row>
     <row r="622" spans="1:6" ht="14.4">
       <c r="A622" s="2" t="s">
-        <v>662</v>
+        <v>630</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C622" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D622" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E622" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E622" s="2" t="s">
+        <v>551</v>
+      </c>
       <c r="F622" s="2" t="s">
-        <v>657</v>
+        <v>552</v>
       </c>
     </row>
     <row r="623" spans="1:6" ht="14.4">
       <c r="A623" s="2" t="s">
-        <v>663</v>
+        <v>631</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C623" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D623" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E623" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E623" s="2" t="s">
+        <v>554</v>
+      </c>
       <c r="F623" s="2" t="s">
-        <v>657</v>
+        <v>555</v>
       </c>
     </row>
     <row r="624" spans="1:6" ht="14.4">
       <c r="A624" s="2" t="s">
-        <v>664</v>
+        <v>632</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C624" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D624" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E624" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E624" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="F624" s="2" t="s">
-        <v>657</v>
+        <v>538</v>
       </c>
     </row>
     <row r="625" spans="1:6" ht="14.4">
       <c r="A625" s="2" t="s">
-        <v>665</v>
+        <v>633</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C625" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D625" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E625" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E625" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="F625" s="2" t="s">
-        <v>657</v>
+        <v>538</v>
       </c>
     </row>
     <row r="626" spans="1:6" ht="14.4">
       <c r="A626" s="2" t="s">
-        <v>666</v>
+        <v>634</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C626" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D626" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E626" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E626" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="F626" s="2" t="s">
-        <v>657</v>
+        <v>538</v>
       </c>
     </row>
     <row r="627" spans="1:6" ht="14.4">
       <c r="A627" s="2" t="s">
-        <v>667</v>
+        <v>635</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C627" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D627" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E627" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E627" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="F627" s="2" t="s">
-        <v>657</v>
+        <v>538</v>
       </c>
     </row>
     <row r="628" spans="1:6" ht="14.4">
       <c r="A628" s="2" t="s">
-        <v>668</v>
+        <v>636</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C628" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D628" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E628" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E628" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="F628" s="2" t="s">
-        <v>657</v>
+        <v>538</v>
       </c>
     </row>
     <row r="629" spans="1:6" ht="14.4">
       <c r="A629" s="2" t="s">
-        <v>669</v>
+        <v>902</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C629" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D629" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E629" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E629" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="F629" s="2" t="s">
-        <v>657</v>
+        <v>538</v>
       </c>
     </row>
     <row r="630" spans="1:6" ht="14.4">
       <c r="A630" s="2" t="s">
-        <v>670</v>
+        <v>903</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C630" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D630" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E630" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E630" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="F630" s="2" t="s">
-        <v>657</v>
+        <v>538</v>
       </c>
     </row>
     <row r="631" spans="1:6" ht="14.4">
       <c r="A631" s="2" t="s">
-        <v>671</v>
+        <v>904</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C631" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D631" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E631" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E631" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="F631" s="2" t="s">
-        <v>657</v>
+        <v>538</v>
       </c>
     </row>
     <row r="632" spans="1:6" ht="14.4">
       <c r="A632" s="2" t="s">
-        <v>672</v>
+        <v>905</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C632" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D632" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E632" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E632" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="F632" s="2" t="s">
-        <v>657</v>
+        <v>538</v>
       </c>
     </row>
     <row r="633" spans="1:6" ht="14.4">
       <c r="A633" s="2" t="s">
-        <v>673</v>
+        <v>645</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C633" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D633" s="2" t="s">
-        <v>656</v>
+        <v>536</v>
       </c>
       <c r="E633" s="2"/>
       <c r="F633" s="2" t="s">
-        <v>657</v>
+        <v>571</v>
       </c>
     </row>
     <row r="634" spans="1:6" ht="14.4">
       <c r="A634" s="2" t="s">
-        <v>674</v>
+        <v>646</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C634" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D634" s="2" t="s">
-        <v>656</v>
+        <v>536</v>
       </c>
       <c r="E634" s="2"/>
       <c r="F634" s="2" t="s">
-        <v>657</v>
+        <v>571</v>
       </c>
     </row>
     <row r="635" spans="1:6" ht="14.4">
       <c r="A635" s="2" t="s">
-        <v>675</v>
+        <v>647</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C635" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D635" s="2" t="s">
-        <v>656</v>
+        <v>536</v>
       </c>
       <c r="E635" s="2"/>
       <c r="F635" s="2" t="s">
-        <v>657</v>
+        <v>571</v>
       </c>
     </row>
     <row r="636" spans="1:6" ht="14.4">
       <c r="A636" s="2" t="s">
-        <v>676</v>
+        <v>650</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C636" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D636" s="2" t="s">
-        <v>656</v>
+        <v>536</v>
       </c>
       <c r="E636" s="2"/>
       <c r="F636" s="2" t="s">
-        <v>657</v>
+        <v>571</v>
       </c>
     </row>
     <row r="637" spans="1:6" ht="14.4">
       <c r="A637" s="2" t="s">
-        <v>677</v>
+        <v>651</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C637" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D637" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E637" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E637" s="2" t="s">
+        <v>554</v>
+      </c>
       <c r="F637" s="2" t="s">
-        <v>657</v>
+        <v>555</v>
       </c>
     </row>
     <row r="638" spans="1:6" ht="14.4">
       <c r="A638" s="2" t="s">
-        <v>678</v>
+        <v>652</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D638" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E638" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E638" s="2" t="s">
+        <v>554</v>
+      </c>
       <c r="F638" s="2" t="s">
-        <v>657</v>
+        <v>555</v>
       </c>
     </row>
     <row r="639" spans="1:6" ht="14.4">
       <c r="A639" s="2" t="s">
-        <v>679</v>
+        <v>908</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D639" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E639" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E639" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F639" s="2" t="s">
-        <v>657</v>
+        <v>545</v>
       </c>
     </row>
     <row r="640" spans="1:6" ht="14.4">
       <c r="A640" s="2" t="s">
-        <v>680</v>
+        <v>909</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C640" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D640" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E640" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E640" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F640" s="2" t="s">
-        <v>657</v>
+        <v>545</v>
       </c>
     </row>
     <row r="641" spans="1:6" ht="14.4">
       <c r="A641" s="2" t="s">
-        <v>681</v>
+        <v>910</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C641" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D641" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E641" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E641" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F641" s="2" t="s">
-        <v>657</v>
+        <v>545</v>
       </c>
     </row>
     <row r="642" spans="1:6" ht="14.4">
       <c r="A642" s="2" t="s">
-        <v>682</v>
+        <v>911</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C642" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D642" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E642" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E642" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F642" s="2" t="s">
-        <v>657</v>
+        <v>545</v>
       </c>
     </row>
     <row r="643" spans="1:6" ht="14.4">
       <c r="A643" s="2" t="s">
-        <v>683</v>
+        <v>637</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C643" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D643" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E643" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E643" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F643" s="2" t="s">
-        <v>657</v>
+        <v>545</v>
       </c>
     </row>
     <row r="644" spans="1:6" ht="14.4">
       <c r="A644" s="2" t="s">
-        <v>684</v>
+        <v>638</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D644" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E644" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E644" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F644" s="2" t="s">
-        <v>657</v>
+        <v>545</v>
       </c>
     </row>
     <row r="645" spans="1:6" ht="14.4">
       <c r="A645" s="2" t="s">
-        <v>685</v>
+        <v>639</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D645" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E645" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E645" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F645" s="2" t="s">
-        <v>657</v>
+        <v>545</v>
       </c>
     </row>
     <row r="646" spans="1:6" ht="14.4">
       <c r="A646" s="2" t="s">
-        <v>686</v>
+        <v>640</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D646" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E646" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E646" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F646" s="2" t="s">
-        <v>657</v>
+        <v>545</v>
       </c>
     </row>
     <row r="647" spans="1:6" ht="14.4">
       <c r="A647" s="2" t="s">
-        <v>687</v>
+        <v>648</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C647" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D647" s="2" t="s">
-        <v>656</v>
+        <v>536</v>
       </c>
       <c r="E647" s="2"/>
       <c r="F647" s="2" t="s">
-        <v>657</v>
+        <v>571</v>
       </c>
     </row>
     <row r="648" spans="1:6" ht="14.4">
       <c r="A648" s="2" t="s">
-        <v>688</v>
+        <v>653</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D648" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E648" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E648" s="2" t="s">
+        <v>554</v>
+      </c>
       <c r="F648" s="2" t="s">
-        <v>657</v>
+        <v>555</v>
       </c>
     </row>
     <row r="649" spans="1:6" ht="14.4">
       <c r="A649" s="2" t="s">
-        <v>689</v>
+        <v>906</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D649" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E649" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E649" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="F649" s="2" t="s">
-        <v>657</v>
+        <v>538</v>
       </c>
     </row>
     <row r="650" spans="1:6" ht="14.4">
       <c r="A650" s="2" t="s">
-        <v>690</v>
+        <v>912</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C650" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D650" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E650" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E650" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F650" s="2" t="s">
-        <v>657</v>
+        <v>545</v>
       </c>
     </row>
     <row r="651" spans="1:6" ht="14.4">
       <c r="A651" s="2" t="s">
-        <v>691</v>
+        <v>641</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C651" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D651" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E651" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E651" s="2" t="s">
+        <v>551</v>
+      </c>
       <c r="F651" s="2" t="s">
-        <v>657</v>
+        <v>552</v>
       </c>
     </row>
     <row r="652" spans="1:6" ht="14.4">
       <c r="A652" s="2" t="s">
-        <v>692</v>
+        <v>642</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C652" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D652" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E652" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E652" s="2" t="s">
+        <v>551</v>
+      </c>
       <c r="F652" s="2" t="s">
-        <v>657</v>
+        <v>552</v>
       </c>
     </row>
     <row r="653" spans="1:6" ht="14.4">
       <c r="A653" s="2" t="s">
-        <v>693</v>
+        <v>643</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D653" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E653" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E653" s="2" t="s">
+        <v>551</v>
+      </c>
       <c r="F653" s="2" t="s">
-        <v>657</v>
+        <v>552</v>
       </c>
     </row>
     <row r="654" spans="1:6" ht="14.4">
       <c r="A654" s="2" t="s">
-        <v>694</v>
+        <v>644</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C654" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D654" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E654" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E654" s="2" t="s">
+        <v>554</v>
+      </c>
       <c r="F654" s="2" t="s">
-        <v>657</v>
+        <v>555</v>
       </c>
     </row>
     <row r="655" spans="1:6" ht="14.4">
       <c r="A655" s="2" t="s">
-        <v>695</v>
+        <v>649</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C655" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D655" s="2" t="s">
-        <v>656</v>
+        <v>536</v>
       </c>
       <c r="E655" s="2"/>
       <c r="F655" s="2" t="s">
-        <v>657</v>
+        <v>571</v>
       </c>
     </row>
     <row r="656" spans="1:6" ht="14.4">
       <c r="A656" s="2" t="s">
-        <v>696</v>
+        <v>654</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C656" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D656" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E656" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E656" s="2" t="s">
+        <v>554</v>
+      </c>
       <c r="F656" s="2" t="s">
-        <v>657</v>
+        <v>555</v>
       </c>
     </row>
     <row r="657" spans="1:6" ht="14.4">
       <c r="A657" s="2" t="s">
-        <v>697</v>
+        <v>907</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C657" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D657" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E657" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E657" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="F657" s="2" t="s">
-        <v>657</v>
+        <v>538</v>
       </c>
     </row>
     <row r="658" spans="1:6" ht="14.4">
       <c r="A658" s="2" t="s">
-        <v>698</v>
+        <v>913</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C658" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D658" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E658" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="E658" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="F658" s="2" t="s">
-        <v>657</v>
+        <v>545</v>
       </c>
     </row>
     <row r="659" spans="1:6" ht="14.4">
       <c r="A659" s="2" t="s">
-        <v>699</v>
+        <v>655</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C659" s="2" t="s">
         <v>8</v>
@@ -15860,10 +15944,10 @@
     </row>
     <row r="660" spans="1:6" ht="14.4">
       <c r="A660" s="2" t="s">
-        <v>700</v>
+        <v>658</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C660" s="2" t="s">
         <v>8</v>
@@ -15878,10 +15962,10 @@
     </row>
     <row r="661" spans="1:6" ht="14.4">
       <c r="A661" s="2" t="s">
-        <v>701</v>
+        <v>659</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C661" s="2" t="s">
         <v>8</v>
@@ -15896,10 +15980,10 @@
     </row>
     <row r="662" spans="1:6" ht="14.4">
       <c r="A662" s="2" t="s">
-        <v>702</v>
+        <v>660</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C662" s="2" t="s">
         <v>8</v>
@@ -15914,10 +15998,10 @@
     </row>
     <row r="663" spans="1:6" ht="14.4">
       <c r="A663" s="2" t="s">
-        <v>703</v>
+        <v>661</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C663" s="2" t="s">
         <v>8</v>
@@ -15932,10 +16016,10 @@
     </row>
     <row r="664" spans="1:6" ht="14.4">
       <c r="A664" s="2" t="s">
-        <v>704</v>
+        <v>662</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C664" s="2" t="s">
         <v>8</v>
@@ -15950,10 +16034,10 @@
     </row>
     <row r="665" spans="1:6" ht="14.4">
       <c r="A665" s="2" t="s">
-        <v>705</v>
+        <v>663</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C665" s="2" t="s">
         <v>8</v>
@@ -15968,10 +16052,10 @@
     </row>
     <row r="666" spans="1:6" ht="14.4">
       <c r="A666" s="2" t="s">
-        <v>706</v>
+        <v>664</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C666" s="2" t="s">
         <v>8</v>
@@ -15986,10 +16070,10 @@
     </row>
     <row r="667" spans="1:6" ht="14.4">
       <c r="A667" s="2" t="s">
-        <v>707</v>
+        <v>665</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C667" s="2" t="s">
         <v>8</v>
@@ -16004,13 +16088,13 @@
     </row>
     <row r="668" spans="1:6" ht="14.4">
       <c r="A668" s="2" t="s">
-        <v>708</v>
+        <v>666</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C668" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D668" s="2" t="s">
         <v>656</v>
@@ -16022,13 +16106,13 @@
     </row>
     <row r="669" spans="1:6" ht="14.4">
       <c r="A669" s="2" t="s">
-        <v>709</v>
+        <v>667</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C669" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D669" s="2" t="s">
         <v>656</v>
@@ -16040,13 +16124,13 @@
     </row>
     <row r="670" spans="1:6" ht="14.4">
       <c r="A670" s="2" t="s">
-        <v>710</v>
+        <v>668</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C670" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D670" s="2" t="s">
         <v>656</v>
@@ -16058,13 +16142,13 @@
     </row>
     <row r="671" spans="1:6" ht="14.4">
       <c r="A671" s="2" t="s">
-        <v>711</v>
+        <v>669</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C671" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D671" s="2" t="s">
         <v>656</v>
@@ -16076,13 +16160,13 @@
     </row>
     <row r="672" spans="1:6" ht="14.4">
       <c r="A672" s="2" t="s">
-        <v>712</v>
+        <v>670</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C672" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D672" s="2" t="s">
         <v>656</v>
@@ -16094,13 +16178,13 @@
     </row>
     <row r="673" spans="1:6" ht="14.4">
       <c r="A673" s="2" t="s">
-        <v>713</v>
+        <v>671</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C673" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D673" s="2" t="s">
         <v>656</v>
@@ -16112,13 +16196,13 @@
     </row>
     <row r="674" spans="1:6" ht="14.4">
       <c r="A674" s="2" t="s">
-        <v>714</v>
+        <v>672</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C674" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D674" s="2" t="s">
         <v>656</v>
@@ -16130,13 +16214,13 @@
     </row>
     <row r="675" spans="1:6" ht="14.4">
       <c r="A675" s="2" t="s">
-        <v>715</v>
+        <v>673</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C675" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D675" s="2" t="s">
         <v>656</v>
@@ -16148,13 +16232,13 @@
     </row>
     <row r="676" spans="1:6" ht="14.4">
       <c r="A676" s="2" t="s">
-        <v>716</v>
+        <v>674</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C676" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D676" s="2" t="s">
         <v>656</v>
@@ -16166,10 +16250,10 @@
     </row>
     <row r="677" spans="1:6" ht="14.4">
       <c r="A677" s="2" t="s">
-        <v>717</v>
+        <v>675</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C677" s="2" t="s">
         <v>8</v>
@@ -16184,10 +16268,10 @@
     </row>
     <row r="678" spans="1:6" ht="14.4">
       <c r="A678" s="2" t="s">
-        <v>718</v>
+        <v>676</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C678" s="2" t="s">
         <v>8</v>
@@ -16202,10 +16286,10 @@
     </row>
     <row r="679" spans="1:6" ht="14.4">
       <c r="A679" s="2" t="s">
-        <v>719</v>
+        <v>677</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C679" s="2" t="s">
         <v>8</v>
@@ -16220,13 +16304,13 @@
     </row>
     <row r="680" spans="1:6" ht="14.4">
       <c r="A680" s="2" t="s">
-        <v>720</v>
+        <v>678</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C680" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D680" s="2" t="s">
         <v>656</v>
@@ -16238,13 +16322,13 @@
     </row>
     <row r="681" spans="1:6" ht="14.4">
       <c r="A681" s="2" t="s">
-        <v>721</v>
+        <v>679</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C681" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D681" s="2" t="s">
         <v>656</v>
@@ -16256,13 +16340,13 @@
     </row>
     <row r="682" spans="1:6" ht="14.4">
       <c r="A682" s="2" t="s">
-        <v>722</v>
+        <v>680</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C682" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D682" s="2" t="s">
         <v>656</v>
@@ -16274,13 +16358,13 @@
     </row>
     <row r="683" spans="1:6" ht="14.4">
       <c r="A683" s="2" t="s">
-        <v>723</v>
+        <v>681</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D683" s="2" t="s">
         <v>656</v>
@@ -16292,13 +16376,13 @@
     </row>
     <row r="684" spans="1:6" ht="14.4">
       <c r="A684" s="2" t="s">
-        <v>724</v>
+        <v>682</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D684" s="2" t="s">
         <v>656</v>
@@ -16310,13 +16394,13 @@
     </row>
     <row r="685" spans="1:6" ht="14.4">
       <c r="A685" s="2" t="s">
-        <v>725</v>
+        <v>683</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C685" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D685" s="2" t="s">
         <v>656</v>
@@ -16328,13 +16412,13 @@
     </row>
     <row r="686" spans="1:6" ht="14.4">
       <c r="A686" s="2" t="s">
-        <v>726</v>
+        <v>684</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C686" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D686" s="2" t="s">
         <v>656</v>
@@ -16346,13 +16430,13 @@
     </row>
     <row r="687" spans="1:6" ht="14.4">
       <c r="A687" s="2" t="s">
-        <v>727</v>
+        <v>685</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C687" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D687" s="2" t="s">
         <v>656</v>
@@ -16364,13 +16448,13 @@
     </row>
     <row r="688" spans="1:6" ht="14.4">
       <c r="A688" s="2" t="s">
-        <v>728</v>
+        <v>686</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C688" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D688" s="2" t="s">
         <v>656</v>
@@ -16382,10 +16466,10 @@
     </row>
     <row r="689" spans="1:6" ht="14.4">
       <c r="A689" s="2" t="s">
-        <v>729</v>
+        <v>687</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C689" s="2" t="s">
         <v>8</v>
@@ -16400,10 +16484,10 @@
     </row>
     <row r="690" spans="1:6" ht="14.4">
       <c r="A690" s="2" t="s">
-        <v>730</v>
+        <v>688</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C690" s="2" t="s">
         <v>8</v>
@@ -16418,10 +16502,10 @@
     </row>
     <row r="691" spans="1:6" ht="14.4">
       <c r="A691" s="2" t="s">
-        <v>731</v>
+        <v>689</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C691" s="2" t="s">
         <v>8</v>
@@ -16436,10 +16520,10 @@
     </row>
     <row r="692" spans="1:6" ht="14.4">
       <c r="A692" s="2" t="s">
-        <v>732</v>
+        <v>690</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C692" s="2" t="s">
         <v>8</v>
@@ -16454,10 +16538,10 @@
     </row>
     <row r="693" spans="1:6" ht="14.4">
       <c r="A693" s="2" t="s">
-        <v>733</v>
+        <v>691</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C693" s="2" t="s">
         <v>8</v>
@@ -16472,10 +16556,10 @@
     </row>
     <row r="694" spans="1:6" ht="14.4">
       <c r="A694" s="2" t="s">
-        <v>734</v>
+        <v>692</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C694" s="2" t="s">
         <v>8</v>
@@ -16490,10 +16574,10 @@
     </row>
     <row r="695" spans="1:6" ht="14.4">
       <c r="A695" s="2" t="s">
-        <v>735</v>
+        <v>693</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C695" s="2" t="s">
         <v>8</v>
@@ -16508,10 +16592,10 @@
     </row>
     <row r="696" spans="1:6" ht="14.4">
       <c r="A696" s="2" t="s">
-        <v>736</v>
+        <v>694</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C696" s="2" t="s">
         <v>8</v>
@@ -16526,10 +16610,10 @@
     </row>
     <row r="697" spans="1:6" ht="14.4">
       <c r="A697" s="2" t="s">
-        <v>737</v>
+        <v>695</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C697" s="2" t="s">
         <v>8</v>
@@ -16544,13 +16628,13 @@
     </row>
     <row r="698" spans="1:6" ht="14.4">
       <c r="A698" s="2" t="s">
-        <v>738</v>
+        <v>696</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D698" s="2" t="s">
         <v>656</v>
@@ -16562,13 +16646,13 @@
     </row>
     <row r="699" spans="1:6" ht="14.4">
       <c r="A699" s="2" t="s">
-        <v>739</v>
+        <v>697</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D699" s="2" t="s">
         <v>656</v>
@@ -16580,13 +16664,13 @@
     </row>
     <row r="700" spans="1:6" ht="14.4">
       <c r="A700" s="2" t="s">
-        <v>740</v>
+        <v>698</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D700" s="2" t="s">
         <v>656</v>
@@ -16598,13 +16682,13 @@
     </row>
     <row r="701" spans="1:6" ht="14.4">
       <c r="A701" s="2" t="s">
-        <v>741</v>
+        <v>699</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D701" s="2" t="s">
         <v>656</v>
@@ -16616,13 +16700,13 @@
     </row>
     <row r="702" spans="1:6" ht="14.4">
       <c r="A702" s="2" t="s">
-        <v>742</v>
+        <v>700</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D702" s="2" t="s">
         <v>656</v>
@@ -16634,13 +16718,13 @@
     </row>
     <row r="703" spans="1:6" ht="14.4">
       <c r="A703" s="2" t="s">
-        <v>743</v>
+        <v>701</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D703" s="2" t="s">
         <v>656</v>
@@ -16652,13 +16736,13 @@
     </row>
     <row r="704" spans="1:6" ht="14.4">
       <c r="A704" s="2" t="s">
-        <v>744</v>
+        <v>702</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D704" s="2" t="s">
         <v>656</v>
@@ -16670,13 +16754,13 @@
     </row>
     <row r="705" spans="1:6" ht="14.4">
       <c r="A705" s="2" t="s">
-        <v>745</v>
+        <v>703</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D705" s="2" t="s">
         <v>656</v>
@@ -16688,13 +16772,13 @@
     </row>
     <row r="706" spans="1:6" ht="14.4">
       <c r="A706" s="2" t="s">
-        <v>746</v>
+        <v>704</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D706" s="2" t="s">
         <v>656</v>
@@ -16706,766 +16790,766 @@
     </row>
     <row r="707" spans="1:6" ht="14.4">
       <c r="A707" s="2" t="s">
-        <v>747</v>
+        <v>705</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C707" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D707" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E707" s="2"/>
       <c r="F707" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="708" spans="1:6" ht="14.4">
       <c r="A708" s="2" t="s">
-        <v>750</v>
+        <v>706</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C708" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D708" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E708" s="2"/>
       <c r="F708" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="709" spans="1:6" ht="14.4">
       <c r="A709" s="2" t="s">
-        <v>751</v>
+        <v>707</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C709" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D709" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E709" s="2"/>
       <c r="F709" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="710" spans="1:6" ht="14.4">
       <c r="A710" s="2" t="s">
-        <v>752</v>
+        <v>708</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D710" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E710" s="2"/>
       <c r="F710" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="711" spans="1:6" ht="14.4">
       <c r="A711" s="2" t="s">
-        <v>753</v>
+        <v>709</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D711" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E711" s="2"/>
       <c r="F711" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="712" spans="1:6" ht="14.4">
       <c r="A712" s="2" t="s">
-        <v>754</v>
+        <v>710</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D712" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E712" s="2"/>
       <c r="F712" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="713" spans="1:6" ht="14.4">
       <c r="A713" s="2" t="s">
-        <v>755</v>
+        <v>711</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D713" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E713" s="2"/>
       <c r="F713" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="714" spans="1:6" ht="14.4">
       <c r="A714" s="2" t="s">
-        <v>756</v>
+        <v>712</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D714" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E714" s="2"/>
       <c r="F714" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="715" spans="1:6" ht="14.4">
       <c r="A715" s="2" t="s">
-        <v>757</v>
+        <v>713</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D715" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E715" s="2"/>
       <c r="F715" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="716" spans="1:6" ht="14.4">
       <c r="A716" s="2" t="s">
-        <v>758</v>
+        <v>714</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D716" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E716" s="2"/>
       <c r="F716" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="717" spans="1:6" ht="14.4">
       <c r="A717" s="2" t="s">
-        <v>759</v>
+        <v>715</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D717" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E717" s="2"/>
       <c r="F717" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="718" spans="1:6" ht="14.4">
       <c r="A718" s="2" t="s">
-        <v>760</v>
+        <v>716</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D718" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E718" s="2"/>
       <c r="F718" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="719" spans="1:6" ht="14.4">
       <c r="A719" s="2" t="s">
-        <v>761</v>
+        <v>717</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C719" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D719" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E719" s="2"/>
       <c r="F719" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="720" spans="1:6" ht="14.4">
       <c r="A720" s="2" t="s">
-        <v>762</v>
+        <v>718</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C720" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D720" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E720" s="2"/>
       <c r="F720" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="721" spans="1:6" ht="14.4">
       <c r="A721" s="2" t="s">
-        <v>763</v>
+        <v>719</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C721" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D721" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E721" s="2"/>
       <c r="F721" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="722" spans="1:6" ht="14.4">
       <c r="A722" s="2" t="s">
-        <v>764</v>
+        <v>720</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C722" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D722" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E722" s="2"/>
       <c r="F722" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="723" spans="1:6" ht="14.4">
       <c r="A723" s="2" t="s">
-        <v>765</v>
+        <v>721</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C723" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D723" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E723" s="2"/>
       <c r="F723" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="724" spans="1:6" ht="14.4">
       <c r="A724" s="2" t="s">
-        <v>766</v>
+        <v>722</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C724" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D724" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E724" s="2"/>
       <c r="F724" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="725" spans="1:6" ht="14.4">
       <c r="A725" s="2" t="s">
-        <v>767</v>
+        <v>723</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C725" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D725" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E725" s="2"/>
       <c r="F725" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="726" spans="1:6" ht="14.4">
       <c r="A726" s="2" t="s">
-        <v>768</v>
+        <v>724</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C726" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D726" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E726" s="2"/>
       <c r="F726" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="727" spans="1:6" ht="14.4">
       <c r="A727" s="2" t="s">
-        <v>769</v>
+        <v>725</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C727" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D727" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E727" s="2"/>
       <c r="F727" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="728" spans="1:6" ht="14.4">
       <c r="A728" s="2" t="s">
-        <v>770</v>
+        <v>726</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D728" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E728" s="2"/>
       <c r="F728" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="729" spans="1:6" ht="14.4">
       <c r="A729" s="2" t="s">
-        <v>771</v>
+        <v>727</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D729" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E729" s="2"/>
       <c r="F729" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="730" spans="1:6" ht="14.4">
       <c r="A730" s="2" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D730" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E730" s="2"/>
       <c r="F730" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="731" spans="1:6" ht="14.4">
       <c r="A731" s="2" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D731" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E731" s="2"/>
       <c r="F731" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="732" spans="1:6" ht="14.4">
       <c r="A732" s="2" t="s">
-        <v>774</v>
+        <v>730</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D732" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E732" s="2"/>
       <c r="F732" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="733" spans="1:6" ht="14.4">
       <c r="A733" s="2" t="s">
-        <v>775</v>
+        <v>731</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D733" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E733" s="2"/>
       <c r="F733" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="734" spans="1:6" ht="14.4">
       <c r="A734" s="2" t="s">
-        <v>776</v>
+        <v>732</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D734" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E734" s="2"/>
       <c r="F734" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="735" spans="1:6" ht="14.4">
       <c r="A735" s="2" t="s">
-        <v>777</v>
+        <v>733</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D735" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E735" s="2"/>
       <c r="F735" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="736" spans="1:6" ht="14.4">
       <c r="A736" s="2" t="s">
-        <v>778</v>
+        <v>734</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D736" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E736" s="2"/>
       <c r="F736" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="737" spans="1:6" ht="14.4">
       <c r="A737" s="2" t="s">
-        <v>779</v>
+        <v>735</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C737" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D737" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E737" s="2"/>
       <c r="F737" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="738" spans="1:6" ht="14.4">
       <c r="A738" s="2" t="s">
-        <v>780</v>
+        <v>736</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D738" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E738" s="2"/>
       <c r="F738" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="739" spans="1:6" ht="14.4">
       <c r="A739" s="2" t="s">
-        <v>781</v>
+        <v>737</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D739" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E739" s="2"/>
       <c r="F739" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="740" spans="1:6" ht="14.4">
       <c r="A740" s="2" t="s">
-        <v>782</v>
+        <v>738</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D740" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E740" s="2"/>
       <c r="F740" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="741" spans="1:6" ht="14.4">
       <c r="A741" s="2" t="s">
-        <v>783</v>
+        <v>739</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C741" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D741" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E741" s="2"/>
       <c r="F741" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="742" spans="1:6" ht="14.4">
       <c r="A742" s="2" t="s">
-        <v>784</v>
+        <v>740</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C742" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D742" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E742" s="2"/>
       <c r="F742" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="743" spans="1:6" ht="14.4">
       <c r="A743" s="2" t="s">
-        <v>785</v>
+        <v>741</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C743" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D743" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E743" s="2"/>
       <c r="F743" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="744" spans="1:6" ht="14.4">
       <c r="A744" s="2" t="s">
-        <v>786</v>
+        <v>742</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C744" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D744" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E744" s="2"/>
       <c r="F744" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="745" spans="1:6" ht="14.4">
       <c r="A745" s="2" t="s">
-        <v>787</v>
+        <v>743</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D745" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E745" s="2"/>
       <c r="F745" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="746" spans="1:6" ht="14.4">
       <c r="A746" s="2" t="s">
-        <v>788</v>
+        <v>744</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D746" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E746" s="2"/>
       <c r="F746" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="747" spans="1:6" ht="14.4">
       <c r="A747" s="2" t="s">
-        <v>789</v>
+        <v>745</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C747" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D747" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E747" s="2"/>
       <c r="F747" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="748" spans="1:6" ht="14.4">
       <c r="A748" s="2" t="s">
-        <v>790</v>
+        <v>746</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C748" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D748" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="E748" s="2"/>
       <c r="F748" s="2" t="s">
-        <v>749</v>
+        <v>657</v>
       </c>
     </row>
     <row r="749" spans="1:6" ht="14.4">
       <c r="A749" s="2" t="s">
-        <v>791</v>
+        <v>747</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C749" s="2" t="s">
         <v>8</v>
@@ -17480,10 +17564,10 @@
     </row>
     <row r="750" spans="1:6" ht="14.4">
       <c r="A750" s="2" t="s">
-        <v>792</v>
+        <v>750</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C750" s="2" t="s">
         <v>8</v>
@@ -17498,10 +17582,10 @@
     </row>
     <row r="751" spans="1:6" ht="14.4">
       <c r="A751" s="2" t="s">
-        <v>793</v>
+        <v>751</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C751" s="2" t="s">
         <v>8</v>
@@ -17516,10 +17600,10 @@
     </row>
     <row r="752" spans="1:6" ht="14.4">
       <c r="A752" s="2" t="s">
-        <v>794</v>
+        <v>752</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C752" s="2" t="s">
         <v>8</v>
@@ -17534,10 +17618,10 @@
     </row>
     <row r="753" spans="1:6" ht="14.4">
       <c r="A753" s="2" t="s">
-        <v>795</v>
+        <v>753</v>
       </c>
       <c r="B753" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C753" s="2" t="s">
         <v>8</v>
@@ -17552,10 +17636,10 @@
     </row>
     <row r="754" spans="1:6" ht="14.4">
       <c r="A754" s="2" t="s">
-        <v>796</v>
+        <v>754</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C754" s="2" t="s">
         <v>8</v>
@@ -17570,10 +17654,10 @@
     </row>
     <row r="755" spans="1:6" ht="14.4">
       <c r="A755" s="2" t="s">
-        <v>797</v>
+        <v>755</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C755" s="2" t="s">
         <v>8</v>
@@ -17588,10 +17672,10 @@
     </row>
     <row r="756" spans="1:6" ht="14.4">
       <c r="A756" s="2" t="s">
-        <v>798</v>
+        <v>756</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C756" s="2" t="s">
         <v>8</v>
@@ -17606,10 +17690,10 @@
     </row>
     <row r="757" spans="1:6" ht="14.4">
       <c r="A757" s="2" t="s">
-        <v>799</v>
+        <v>757</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C757" s="2" t="s">
         <v>8</v>
@@ -17624,10 +17708,10 @@
     </row>
     <row r="758" spans="1:6" ht="14.4">
       <c r="A758" s="2" t="s">
-        <v>800</v>
+        <v>758</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C758" s="2" t="s">
         <v>8</v>
@@ -17642,10 +17726,10 @@
     </row>
     <row r="759" spans="1:6" ht="14.4">
       <c r="A759" s="2" t="s">
-        <v>801</v>
+        <v>759</v>
       </c>
       <c r="B759" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C759" s="2" t="s">
         <v>8</v>
@@ -17660,10 +17744,10 @@
     </row>
     <row r="760" spans="1:6" ht="14.4">
       <c r="A760" s="2" t="s">
-        <v>802</v>
+        <v>760</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C760" s="2" t="s">
         <v>8</v>
@@ -17678,10 +17762,10 @@
     </row>
     <row r="761" spans="1:6" ht="14.4">
       <c r="A761" s="2" t="s">
-        <v>803</v>
+        <v>761</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C761" s="2" t="s">
         <v>8</v>
@@ -17696,10 +17780,10 @@
     </row>
     <row r="762" spans="1:6" ht="14.4">
       <c r="A762" s="2" t="s">
-        <v>804</v>
+        <v>762</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C762" s="2" t="s">
         <v>8</v>
@@ -17714,10 +17798,10 @@
     </row>
     <row r="763" spans="1:6" ht="14.4">
       <c r="A763" s="2" t="s">
-        <v>805</v>
+        <v>763</v>
       </c>
       <c r="B763" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C763" s="2" t="s">
         <v>8</v>
@@ -17732,10 +17816,10 @@
     </row>
     <row r="764" spans="1:6" ht="14.4">
       <c r="A764" s="2" t="s">
-        <v>806</v>
+        <v>764</v>
       </c>
       <c r="B764" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C764" s="2" t="s">
         <v>8</v>
@@ -17750,10 +17834,10 @@
     </row>
     <row r="765" spans="1:6" ht="14.4">
       <c r="A765" s="2" t="s">
-        <v>807</v>
+        <v>765</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C765" s="2" t="s">
         <v>8</v>
@@ -17768,10 +17852,10 @@
     </row>
     <row r="766" spans="1:6" ht="14.4">
       <c r="A766" s="2" t="s">
-        <v>808</v>
+        <v>766</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C766" s="2" t="s">
         <v>8</v>
@@ -17786,10 +17870,10 @@
     </row>
     <row r="767" spans="1:6" ht="14.4">
       <c r="A767" s="2" t="s">
-        <v>809</v>
+        <v>767</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C767" s="2" t="s">
         <v>8</v>
@@ -17804,10 +17888,10 @@
     </row>
     <row r="768" spans="1:6" ht="14.4">
       <c r="A768" s="2" t="s">
-        <v>810</v>
+        <v>768</v>
       </c>
       <c r="B768" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C768" s="2" t="s">
         <v>8</v>
@@ -17822,13 +17906,13 @@
     </row>
     <row r="769" spans="1:6" ht="14.4">
       <c r="A769" s="2" t="s">
-        <v>811</v>
+        <v>769</v>
       </c>
       <c r="B769" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C769" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D769" s="2" t="s">
         <v>748</v>
@@ -17840,10 +17924,10 @@
     </row>
     <row r="770" spans="1:6" ht="14.4">
       <c r="A770" s="2" t="s">
-        <v>812</v>
+        <v>770</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C770" s="2" t="s">
         <v>34</v>
@@ -17858,10 +17942,10 @@
     </row>
     <row r="771" spans="1:6" ht="14.4">
       <c r="A771" s="2" t="s">
-        <v>813</v>
+        <v>771</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C771" s="2" t="s">
         <v>34</v>
@@ -17876,10 +17960,10 @@
     </row>
     <row r="772" spans="1:6" ht="14.4">
       <c r="A772" s="2" t="s">
-        <v>814</v>
+        <v>772</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C772" s="2" t="s">
         <v>34</v>
@@ -17894,13 +17978,13 @@
     </row>
     <row r="773" spans="1:6" ht="14.4">
       <c r="A773" s="2" t="s">
-        <v>815</v>
+        <v>773</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D773" s="2" t="s">
         <v>748</v>
@@ -17912,10 +17996,10 @@
     </row>
     <row r="774" spans="1:6" ht="14.4">
       <c r="A774" s="2" t="s">
-        <v>816</v>
+        <v>774</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C774" s="2" t="s">
         <v>40</v>
@@ -17930,10 +18014,10 @@
     </row>
     <row r="775" spans="1:6" ht="14.4">
       <c r="A775" s="2" t="s">
-        <v>817</v>
+        <v>775</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C775" s="2" t="s">
         <v>40</v>
@@ -17948,10 +18032,10 @@
     </row>
     <row r="776" spans="1:6" ht="14.4">
       <c r="A776" s="2" t="s">
-        <v>818</v>
+        <v>776</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C776" s="2" t="s">
         <v>40</v>
@@ -17966,10 +18050,10 @@
     </row>
     <row r="777" spans="1:6" ht="14.4">
       <c r="A777" s="2" t="s">
-        <v>819</v>
+        <v>777</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C777" s="2" t="s">
         <v>40</v>
@@ -17984,13 +18068,13 @@
     </row>
     <row r="778" spans="1:6" ht="14.4">
       <c r="A778" s="2" t="s">
-        <v>820</v>
+        <v>778</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C778" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D778" s="2" t="s">
         <v>748</v>
@@ -18002,13 +18086,13 @@
     </row>
     <row r="779" spans="1:6" ht="14.4">
       <c r="A779" s="2" t="s">
-        <v>821</v>
+        <v>779</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C779" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D779" s="2" t="s">
         <v>748</v>
@@ -18020,13 +18104,13 @@
     </row>
     <row r="780" spans="1:6" ht="14.4">
       <c r="A780" s="2" t="s">
-        <v>822</v>
+        <v>780</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C780" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D780" s="2" t="s">
         <v>748</v>
@@ -18038,13 +18122,13 @@
     </row>
     <row r="781" spans="1:6" ht="14.4">
       <c r="A781" s="2" t="s">
-        <v>823</v>
+        <v>781</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C781" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D781" s="2" t="s">
         <v>748</v>
@@ -18056,10 +18140,10 @@
     </row>
     <row r="782" spans="1:6" ht="14.4">
       <c r="A782" s="2" t="s">
-        <v>824</v>
+        <v>782</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C782" s="2" t="s">
         <v>8</v>
@@ -18074,13 +18158,13 @@
     </row>
     <row r="783" spans="1:6" ht="14.4">
       <c r="A783" s="2" t="s">
-        <v>825</v>
+        <v>783</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C783" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D783" s="2" t="s">
         <v>748</v>
@@ -18092,13 +18176,13 @@
     </row>
     <row r="784" spans="1:6" ht="14.4">
       <c r="A784" s="2" t="s">
-        <v>826</v>
+        <v>784</v>
       </c>
       <c r="B784" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C784" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D784" s="2" t="s">
         <v>748</v>
@@ -18110,13 +18194,13 @@
     </row>
     <row r="785" spans="1:6" ht="14.4">
       <c r="A785" s="2" t="s">
-        <v>827</v>
+        <v>785</v>
       </c>
       <c r="B785" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C785" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D785" s="2" t="s">
         <v>748</v>
@@ -18128,10 +18212,10 @@
     </row>
     <row r="786" spans="1:6" ht="14.4">
       <c r="A786" s="2" t="s">
-        <v>828</v>
+        <v>786</v>
       </c>
       <c r="B786" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C786" s="2" t="s">
         <v>8</v>
@@ -18146,13 +18230,13 @@
     </row>
     <row r="787" spans="1:6" ht="14.4">
       <c r="A787" s="2" t="s">
-        <v>829</v>
+        <v>787</v>
       </c>
       <c r="B787" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C787" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D787" s="2" t="s">
         <v>748</v>
@@ -18164,13 +18248,13 @@
     </row>
     <row r="788" spans="1:6" ht="14.4">
       <c r="A788" s="2" t="s">
-        <v>830</v>
+        <v>788</v>
       </c>
       <c r="B788" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C788" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D788" s="2" t="s">
         <v>748</v>
@@ -18182,13 +18266,13 @@
     </row>
     <row r="789" spans="1:6" ht="14.4">
       <c r="A789" s="2" t="s">
-        <v>831</v>
+        <v>789</v>
       </c>
       <c r="B789" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C789" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D789" s="2" t="s">
         <v>748</v>
@@ -18200,10 +18284,10 @@
     </row>
     <row r="790" spans="1:6" ht="14.4">
       <c r="A790" s="2" t="s">
-        <v>832</v>
+        <v>790</v>
       </c>
       <c r="B790" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C790" s="2" t="s">
         <v>8</v>
@@ -18218,10 +18302,10 @@
     </row>
     <row r="791" spans="1:6" ht="14.4">
       <c r="A791" s="2" t="s">
-        <v>833</v>
+        <v>791</v>
       </c>
       <c r="B791" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C791" s="2" t="s">
         <v>8</v>
@@ -18236,10 +18320,10 @@
     </row>
     <row r="792" spans="1:6" ht="14.4">
       <c r="A792" s="2" t="s">
-        <v>834</v>
+        <v>792</v>
       </c>
       <c r="B792" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C792" s="2" t="s">
         <v>8</v>
@@ -18254,10 +18338,10 @@
     </row>
     <row r="793" spans="1:6" ht="14.4">
       <c r="A793" s="2" t="s">
-        <v>835</v>
+        <v>793</v>
       </c>
       <c r="B793" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C793" s="2" t="s">
         <v>8</v>
@@ -18272,10 +18356,10 @@
     </row>
     <row r="794" spans="1:6" ht="14.4">
       <c r="A794" s="2" t="s">
-        <v>836</v>
+        <v>794</v>
       </c>
       <c r="B794" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C794" s="2" t="s">
         <v>8</v>
@@ -18290,10 +18374,10 @@
     </row>
     <row r="795" spans="1:6" ht="14.4">
       <c r="A795" s="2" t="s">
-        <v>837</v>
+        <v>795</v>
       </c>
       <c r="B795" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C795" s="2" t="s">
         <v>8</v>
@@ -18308,10 +18392,10 @@
     </row>
     <row r="796" spans="1:6" ht="14.4">
       <c r="A796" s="2" t="s">
-        <v>838</v>
+        <v>796</v>
       </c>
       <c r="B796" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C796" s="2" t="s">
         <v>8</v>
@@ -18326,10 +18410,10 @@
     </row>
     <row r="797" spans="1:6" ht="14.4">
       <c r="A797" s="2" t="s">
-        <v>839</v>
+        <v>797</v>
       </c>
       <c r="B797" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C797" s="2" t="s">
         <v>8</v>
@@ -18344,10 +18428,10 @@
     </row>
     <row r="798" spans="1:6" ht="14.4">
       <c r="A798" s="2" t="s">
-        <v>840</v>
+        <v>798</v>
       </c>
       <c r="B798" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C798" s="2" t="s">
         <v>8</v>
@@ -18362,10 +18446,10 @@
     </row>
     <row r="799" spans="1:6" ht="14.4">
       <c r="A799" s="2" t="s">
-        <v>841</v>
+        <v>799</v>
       </c>
       <c r="B799" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C799" s="2" t="s">
         <v>8</v>
@@ -18380,10 +18464,10 @@
     </row>
     <row r="800" spans="1:6" ht="14.4">
       <c r="A800" s="2" t="s">
-        <v>842</v>
+        <v>800</v>
       </c>
       <c r="B800" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C800" s="2" t="s">
         <v>8</v>
@@ -18398,10 +18482,10 @@
     </row>
     <row r="801" spans="1:6" ht="14.4">
       <c r="A801" s="2" t="s">
-        <v>843</v>
+        <v>801</v>
       </c>
       <c r="B801" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C801" s="2" t="s">
         <v>8</v>
@@ -18416,10 +18500,10 @@
     </row>
     <row r="802" spans="1:6" ht="14.4">
       <c r="A802" s="2" t="s">
-        <v>844</v>
+        <v>802</v>
       </c>
       <c r="B802" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C802" s="2" t="s">
         <v>8</v>
@@ -18434,10 +18518,10 @@
     </row>
     <row r="803" spans="1:6" ht="14.4">
       <c r="A803" s="2" t="s">
-        <v>845</v>
+        <v>803</v>
       </c>
       <c r="B803" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C803" s="2" t="s">
         <v>8</v>
@@ -18452,10 +18536,10 @@
     </row>
     <row r="804" spans="1:6" ht="14.4">
       <c r="A804" s="2" t="s">
-        <v>846</v>
+        <v>804</v>
       </c>
       <c r="B804" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C804" s="2" t="s">
         <v>8</v>
@@ -18470,10 +18554,10 @@
     </row>
     <row r="805" spans="1:6" ht="14.4">
       <c r="A805" s="2" t="s">
-        <v>847</v>
+        <v>805</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C805" s="2" t="s">
         <v>8</v>
@@ -18488,10 +18572,10 @@
     </row>
     <row r="806" spans="1:6" ht="14.4">
       <c r="A806" s="2" t="s">
-        <v>848</v>
+        <v>806</v>
       </c>
       <c r="B806" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C806" s="2" t="s">
         <v>8</v>
@@ -18506,10 +18590,10 @@
     </row>
     <row r="807" spans="1:6" ht="14.4">
       <c r="A807" s="2" t="s">
-        <v>849</v>
+        <v>807</v>
       </c>
       <c r="B807" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C807" s="2" t="s">
         <v>8</v>
@@ -18524,10 +18608,10 @@
     </row>
     <row r="808" spans="1:6" ht="14.4">
       <c r="A808" s="2" t="s">
-        <v>850</v>
+        <v>808</v>
       </c>
       <c r="B808" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C808" s="2" t="s">
         <v>8</v>
@@ -18542,10 +18626,10 @@
     </row>
     <row r="809" spans="1:6" ht="14.4">
       <c r="A809" s="2" t="s">
-        <v>851</v>
+        <v>809</v>
       </c>
       <c r="B809" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C809" s="2" t="s">
         <v>8</v>
@@ -18560,13 +18644,13 @@
     </row>
     <row r="810" spans="1:6" ht="14.4">
       <c r="A810" s="2" t="s">
-        <v>852</v>
+        <v>810</v>
       </c>
       <c r="B810" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C810" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D810" s="2" t="s">
         <v>748</v>
@@ -18578,10 +18662,10 @@
     </row>
     <row r="811" spans="1:6" ht="14.4">
       <c r="A811" s="2" t="s">
-        <v>853</v>
+        <v>811</v>
       </c>
       <c r="B811" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C811" s="2" t="s">
         <v>34</v>
@@ -18596,10 +18680,10 @@
     </row>
     <row r="812" spans="1:6" ht="14.4">
       <c r="A812" s="2" t="s">
-        <v>854</v>
+        <v>812</v>
       </c>
       <c r="B812" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C812" s="2" t="s">
         <v>34</v>
@@ -18614,10 +18698,10 @@
     </row>
     <row r="813" spans="1:6" ht="14.4">
       <c r="A813" s="2" t="s">
-        <v>855</v>
+        <v>813</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>34</v>
@@ -18632,13 +18716,13 @@
     </row>
     <row r="814" spans="1:6" ht="14.4">
       <c r="A814" s="2" t="s">
-        <v>856</v>
+        <v>814</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C814" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D814" s="2" t="s">
         <v>748</v>
@@ -18650,10 +18734,10 @@
     </row>
     <row r="815" spans="1:6" ht="14.4">
       <c r="A815" s="2" t="s">
-        <v>857</v>
+        <v>815</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C815" s="2" t="s">
         <v>40</v>
@@ -18668,10 +18752,10 @@
     </row>
     <row r="816" spans="1:6" ht="14.4">
       <c r="A816" s="2" t="s">
-        <v>858</v>
+        <v>816</v>
       </c>
       <c r="B816" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C816" s="2" t="s">
         <v>40</v>
@@ -18686,10 +18770,10 @@
     </row>
     <row r="817" spans="1:6" ht="14.4">
       <c r="A817" s="2" t="s">
-        <v>859</v>
+        <v>817</v>
       </c>
       <c r="B817" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C817" s="2" t="s">
         <v>40</v>
@@ -18704,10 +18788,10 @@
     </row>
     <row r="818" spans="1:6" ht="14.4">
       <c r="A818" s="2" t="s">
-        <v>860</v>
+        <v>818</v>
       </c>
       <c r="B818" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C818" s="2" t="s">
         <v>40</v>
@@ -18722,13 +18806,13 @@
     </row>
     <row r="819" spans="1:6" ht="14.4">
       <c r="A819" s="2" t="s">
-        <v>861</v>
+        <v>819</v>
       </c>
       <c r="B819" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C819" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D819" s="2" t="s">
         <v>748</v>
@@ -18740,13 +18824,13 @@
     </row>
     <row r="820" spans="1:6" ht="14.4">
       <c r="A820" s="2" t="s">
-        <v>862</v>
+        <v>820</v>
       </c>
       <c r="B820" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C820" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D820" s="2" t="s">
         <v>748</v>
@@ -18758,13 +18842,13 @@
     </row>
     <row r="821" spans="1:6" ht="14.4">
       <c r="A821" s="2" t="s">
-        <v>863</v>
+        <v>821</v>
       </c>
       <c r="B821" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C821" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D821" s="2" t="s">
         <v>748</v>
@@ -18776,13 +18860,13 @@
     </row>
     <row r="822" spans="1:6" ht="14.4">
       <c r="A822" s="2" t="s">
-        <v>864</v>
+        <v>822</v>
       </c>
       <c r="B822" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C822" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D822" s="2" t="s">
         <v>748</v>
@@ -18794,10 +18878,10 @@
     </row>
     <row r="823" spans="1:6" ht="14.4">
       <c r="A823" s="2" t="s">
-        <v>865</v>
+        <v>823</v>
       </c>
       <c r="B823" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C823" s="2" t="s">
         <v>8</v>
@@ -18812,13 +18896,13 @@
     </row>
     <row r="824" spans="1:6" ht="14.4">
       <c r="A824" s="2" t="s">
-        <v>866</v>
+        <v>824</v>
       </c>
       <c r="B824" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C824" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D824" s="2" t="s">
         <v>748</v>
@@ -18830,13 +18914,13 @@
     </row>
     <row r="825" spans="1:6" ht="14.4">
       <c r="A825" s="2" t="s">
-        <v>867</v>
+        <v>825</v>
       </c>
       <c r="B825" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C825" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D825" s="2" t="s">
         <v>748</v>
@@ -18848,13 +18932,13 @@
     </row>
     <row r="826" spans="1:6" ht="14.4">
       <c r="A826" s="2" t="s">
-        <v>868</v>
+        <v>826</v>
       </c>
       <c r="B826" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C826" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D826" s="2" t="s">
         <v>748</v>
@@ -18866,10 +18950,10 @@
     </row>
     <row r="827" spans="1:6" ht="14.4">
       <c r="A827" s="2" t="s">
-        <v>869</v>
+        <v>827</v>
       </c>
       <c r="B827" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C827" s="2" t="s">
         <v>8</v>
@@ -18884,13 +18968,13 @@
     </row>
     <row r="828" spans="1:6" ht="14.4">
       <c r="A828" s="2" t="s">
-        <v>870</v>
+        <v>828</v>
       </c>
       <c r="B828" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C828" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D828" s="2" t="s">
         <v>748</v>
@@ -18902,13 +18986,13 @@
     </row>
     <row r="829" spans="1:6" ht="14.4">
       <c r="A829" s="2" t="s">
-        <v>871</v>
+        <v>829</v>
       </c>
       <c r="B829" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C829" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D829" s="2" t="s">
         <v>748</v>
@@ -18920,627 +19004,565 @@
     </row>
     <row r="830" spans="1:6" ht="14.4">
       <c r="A830" s="2" t="s">
-        <v>872</v>
+        <v>830</v>
       </c>
       <c r="B830" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C830" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D830" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E830" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E830" s="2"/>
       <c r="F830" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="831" spans="1:6" ht="14.4">
       <c r="A831" s="2" t="s">
-        <v>873</v>
+        <v>831</v>
       </c>
       <c r="B831" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C831" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D831" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E831" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E831" s="2"/>
       <c r="F831" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="832" spans="1:6" ht="14.4">
       <c r="A832" s="2" t="s">
-        <v>874</v>
+        <v>832</v>
       </c>
       <c r="B832" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C832" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D832" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E832" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E832" s="2"/>
       <c r="F832" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="833" spans="1:6" ht="14.4">
       <c r="A833" s="2" t="s">
-        <v>875</v>
+        <v>833</v>
       </c>
       <c r="B833" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C833" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D833" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E833" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E833" s="2"/>
       <c r="F833" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="834" spans="1:6" ht="14.4">
       <c r="A834" s="2" t="s">
-        <v>876</v>
+        <v>834</v>
       </c>
       <c r="B834" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C834" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D834" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E834" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E834" s="2"/>
       <c r="F834" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="835" spans="1:6" ht="14.4">
       <c r="A835" s="2" t="s">
-        <v>877</v>
+        <v>835</v>
       </c>
       <c r="B835" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C835" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D835" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E835" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E835" s="2"/>
       <c r="F835" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="836" spans="1:6" ht="14.4">
       <c r="A836" s="2" t="s">
-        <v>878</v>
+        <v>836</v>
       </c>
       <c r="B836" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C836" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D836" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E836" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E836" s="2"/>
       <c r="F836" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="837" spans="1:6" ht="14.4">
       <c r="A837" s="2" t="s">
-        <v>879</v>
+        <v>837</v>
       </c>
       <c r="B837" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C837" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D837" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E837" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E837" s="2"/>
       <c r="F837" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="838" spans="1:6" ht="14.4">
       <c r="A838" s="2" t="s">
-        <v>880</v>
+        <v>838</v>
       </c>
       <c r="B838" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C838" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D838" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E838" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E838" s="2"/>
       <c r="F838" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="839" spans="1:6" ht="14.4">
       <c r="A839" s="2" t="s">
-        <v>881</v>
+        <v>839</v>
       </c>
       <c r="B839" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C839" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D839" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E839" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E839" s="2"/>
       <c r="F839" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="840" spans="1:6" ht="14.4">
       <c r="A840" s="2" t="s">
-        <v>882</v>
+        <v>840</v>
       </c>
       <c r="B840" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C840" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D840" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E840" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E840" s="2"/>
       <c r="F840" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="841" spans="1:6" ht="14.4">
       <c r="A841" s="2" t="s">
-        <v>883</v>
+        <v>841</v>
       </c>
       <c r="B841" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C841" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D841" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E841" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E841" s="2"/>
       <c r="F841" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="842" spans="1:6" ht="14.4">
       <c r="A842" s="2" t="s">
-        <v>884</v>
+        <v>842</v>
       </c>
       <c r="B842" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C842" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D842" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E842" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E842" s="2"/>
       <c r="F842" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="843" spans="1:6" ht="14.4">
       <c r="A843" s="2" t="s">
-        <v>885</v>
+        <v>843</v>
       </c>
       <c r="B843" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C843" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D843" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E843" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E843" s="2"/>
       <c r="F843" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="844" spans="1:6" ht="14.4">
       <c r="A844" s="2" t="s">
-        <v>886</v>
+        <v>844</v>
       </c>
       <c r="B844" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C844" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D844" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E844" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E844" s="2"/>
       <c r="F844" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="845" spans="1:6" ht="14.4">
       <c r="A845" s="2" t="s">
-        <v>887</v>
+        <v>845</v>
       </c>
       <c r="B845" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C845" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D845" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E845" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E845" s="2"/>
       <c r="F845" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="846" spans="1:6" ht="14.4">
       <c r="A846" s="2" t="s">
-        <v>888</v>
+        <v>846</v>
       </c>
       <c r="B846" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C846" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D846" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E846" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E846" s="2"/>
       <c r="F846" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="847" spans="1:6" ht="14.4">
       <c r="A847" s="2" t="s">
-        <v>889</v>
+        <v>847</v>
       </c>
       <c r="B847" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C847" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D847" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E847" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E847" s="2"/>
       <c r="F847" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="848" spans="1:6" ht="14.4">
       <c r="A848" s="2" t="s">
-        <v>890</v>
+        <v>848</v>
       </c>
       <c r="B848" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C848" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D848" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E848" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E848" s="2"/>
       <c r="F848" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="849" spans="1:6" ht="14.4">
       <c r="A849" s="2" t="s">
-        <v>891</v>
+        <v>849</v>
       </c>
       <c r="B849" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C849" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D849" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E849" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E849" s="2"/>
       <c r="F849" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="850" spans="1:6" ht="14.4">
       <c r="A850" s="2" t="s">
-        <v>892</v>
+        <v>850</v>
       </c>
       <c r="B850" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C850" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D850" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E850" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E850" s="2"/>
       <c r="F850" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="851" spans="1:6" ht="14.4">
       <c r="A851" s="2" t="s">
-        <v>893</v>
+        <v>851</v>
       </c>
       <c r="B851" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C851" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D851" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E851" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E851" s="2"/>
       <c r="F851" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="852" spans="1:6" ht="14.4">
       <c r="A852" s="2" t="s">
-        <v>894</v>
+        <v>852</v>
       </c>
       <c r="B852" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C852" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D852" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E852" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E852" s="2"/>
       <c r="F852" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="853" spans="1:6" ht="14.4">
       <c r="A853" s="2" t="s">
-        <v>895</v>
+        <v>853</v>
       </c>
       <c r="B853" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C853" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D853" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E853" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E853" s="2"/>
       <c r="F853" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="854" spans="1:6" ht="14.4">
       <c r="A854" s="2" t="s">
-        <v>896</v>
+        <v>854</v>
       </c>
       <c r="B854" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C854" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D854" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E854" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E854" s="2"/>
       <c r="F854" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="855" spans="1:6" ht="14.4">
       <c r="A855" s="2" t="s">
-        <v>897</v>
+        <v>855</v>
       </c>
       <c r="B855" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C855" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D855" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E855" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E855" s="2"/>
       <c r="F855" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="856" spans="1:6" ht="14.4">
       <c r="A856" s="2" t="s">
-        <v>898</v>
+        <v>856</v>
       </c>
       <c r="B856" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C856" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D856" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E856" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E856" s="2"/>
       <c r="F856" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="857" spans="1:6" ht="14.4">
       <c r="A857" s="2" t="s">
-        <v>899</v>
+        <v>857</v>
       </c>
       <c r="B857" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C857" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D857" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E857" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E857" s="2"/>
       <c r="F857" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="858" spans="1:6" ht="14.4">
       <c r="A858" s="2" t="s">
-        <v>900</v>
+        <v>858</v>
       </c>
       <c r="B858" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C858" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D858" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E858" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E858" s="2"/>
       <c r="F858" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="859" spans="1:6" ht="14.4">
       <c r="A859" s="2" t="s">
-        <v>901</v>
+        <v>859</v>
       </c>
       <c r="B859" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C859" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D859" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E859" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E859" s="2"/>
       <c r="F859" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="860" spans="1:6" ht="14.4">
       <c r="A860" s="2" t="s">
-        <v>902</v>
+        <v>860</v>
       </c>
       <c r="B860" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C860" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D860" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E860" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E860" s="2"/>
       <c r="F860" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="861" spans="1:6" ht="14.4">
       <c r="A861" s="2" t="s">
-        <v>903</v>
+        <v>861</v>
       </c>
       <c r="B861" s="2" t="s">
         <v>80</v>
@@ -19549,138 +19571,124 @@
         <v>8</v>
       </c>
       <c r="D861" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E861" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E861" s="2"/>
       <c r="F861" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="862" spans="1:6" ht="14.4">
       <c r="A862" s="2" t="s">
-        <v>904</v>
+        <v>862</v>
       </c>
       <c r="B862" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C862" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D862" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E862" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E862" s="2"/>
       <c r="F862" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="863" spans="1:6" ht="14.4">
       <c r="A863" s="2" t="s">
-        <v>905</v>
+        <v>863</v>
       </c>
       <c r="B863" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C863" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D863" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E863" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E863" s="2"/>
       <c r="F863" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="864" spans="1:6" ht="14.4">
       <c r="A864" s="2" t="s">
-        <v>906</v>
+        <v>864</v>
       </c>
       <c r="B864" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C864" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D864" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E864" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E864" s="2"/>
       <c r="F864" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="865" spans="1:6" ht="14.4">
       <c r="A865" s="2" t="s">
-        <v>907</v>
+        <v>865</v>
       </c>
       <c r="B865" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C865" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D865" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E865" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E865" s="2"/>
       <c r="F865" s="2" t="s">
-        <v>538</v>
+        <v>749</v>
       </c>
     </row>
     <row r="866" spans="1:6" ht="14.4">
       <c r="A866" s="2" t="s">
-        <v>908</v>
+        <v>866</v>
       </c>
       <c r="B866" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C866" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D866" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E866" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E866" s="2"/>
       <c r="F866" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="867" spans="1:6" ht="14.4">
       <c r="A867" s="2" t="s">
-        <v>909</v>
+        <v>867</v>
       </c>
       <c r="B867" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C867" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D867" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E867" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E867" s="2"/>
       <c r="F867" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="868" spans="1:6" ht="14.4">
       <c r="A868" s="2" t="s">
-        <v>910</v>
+        <v>868</v>
       </c>
       <c r="B868" s="2" t="s">
         <v>80</v>
@@ -19689,18 +19697,16 @@
         <v>8</v>
       </c>
       <c r="D868" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E868" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E868" s="2"/>
       <c r="F868" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="869" spans="1:6" ht="14.4">
       <c r="A869" s="2" t="s">
-        <v>911</v>
+        <v>869</v>
       </c>
       <c r="B869" s="2" t="s">
         <v>80</v>
@@ -19709,18 +19715,16 @@
         <v>8</v>
       </c>
       <c r="D869" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E869" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E869" s="2"/>
       <c r="F869" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="870" spans="1:6" ht="14.4">
       <c r="A870" s="2" t="s">
-        <v>912</v>
+        <v>870</v>
       </c>
       <c r="B870" s="2" t="s">
         <v>80</v>
@@ -19729,18 +19733,16 @@
         <v>34</v>
       </c>
       <c r="D870" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E870" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E870" s="2"/>
       <c r="F870" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="871" spans="1:6" ht="14.4">
       <c r="A871" s="2" t="s">
-        <v>913</v>
+        <v>871</v>
       </c>
       <c r="B871" s="2" t="s">
         <v>80</v>
@@ -19749,13 +19751,11 @@
         <v>40</v>
       </c>
       <c r="D871" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E871" s="2" t="s">
-        <v>544</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="E871" s="2"/>
       <c r="F871" s="2" t="s">
-        <v>545</v>
+        <v>749</v>
       </c>
     </row>
     <row r="872" spans="1:6" ht="14.4" customHeight="1">
